--- a/tdsurvivor/Assets/Excels/SpawnerConfig.xlsx
+++ b/tdsurvivor/Assets/Excels/SpawnerConfig.xlsx
@@ -56,7 +56,7 @@
     <t>portals</t>
   </si>
   <si>
-    <t>[0,1,2,3,4,5,6,7,8,9,10,11]</t>
+    <t>[0,1,2,3,4,5]</t>
   </si>
 </sst>
 </file>
@@ -557,7 +557,7 @@
     <col min="9" max="9" width="20.71094" customWidth="1"/>
     <col min="10" max="10" width="18.85547" customWidth="1"/>
     <col min="11" max="11" width="17.85547" customWidth="1"/>
-    <col min="12" max="12" width="24.57031" customWidth="1"/>
+    <col min="12" max="12" width="14.71094" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">

--- a/tdsurvivor/Assets/Excels/SpawnerConfig.xlsx
+++ b/tdsurvivor/Assets/Excels/SpawnerConfig.xlsx
@@ -626,7 +626,7 @@
         <v>1001</v>
       </c>
       <c r="D2" s="5">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="E2" s="5">
         <v>1</v>
@@ -664,7 +664,7 @@
         <v>1001</v>
       </c>
       <c r="D3" s="5">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="E3" s="5">
         <v>1</v>
@@ -702,7 +702,7 @@
         <v>1001</v>
       </c>
       <c r="D4" s="5">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="E4" s="5">
         <v>1</v>
@@ -740,7 +740,7 @@
         <v>1001</v>
       </c>
       <c r="D5" s="5">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
